--- a/astro-site/public/dl/guia-chocolateria-obrador/capacidad-obrador-y-clima.xlsx
+++ b/astro-site/public/dl/guia-chocolateria-obrador/capacidad-obrador-y-clima.xlsx
@@ -271,7 +271,7 @@
   <commentList>
     <comment ref="A24" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (El encabezado del Anexo dice: «Las siguientes actividades se han identificado con las claves y en los términos estab... · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
+        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (El encabezado del Anexo dice: «Las siguientes actividades se han identificado con las claves y en...) · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
       </text>
     </comment>
   </commentList>
@@ -326,7 +326,7 @@
   <commentList>
     <comment ref="J10" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Dos límites del propio texto: queda fuera lo que tenga impacto en el patrimonio histórico-artístico o en el uso priv... · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
+        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Arts.) · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
       </text>
     </comment>
     <comment ref="J11" authorId="0" shapeId="0">
@@ -351,7 +351,7 @@
     </comment>
     <comment ref="J13" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Enumerados los 55 grupos del Anexo: 435, 439, 442, 452, 454, 474, 491, 495, 615, 641-647, 651-659, 662, 665, 691, 75... · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
+        <t>Verificado el 12-09-2026 · Ley 12/2012, de 26 de diciembre, de medidas urgentes de liberalización del comercio y de determinados servicios (BOE-A-2012-15595), texto consolidado · «Última modificación: 29... (Enumerados los 55 grupos del Anexo: 435, 439, 442, 452, 454, 474, 491, 495, 615, 641-647, 651-659, 662, 665,...) · https://www.boe.es/buscar/act.php?id=BOE-A-2012-15595</t>
       </text>
     </comment>
     <comment ref="J22" authorId="0" shapeId="0">
